--- a/src/test/resources/TestDataFolder/Premium_Sauce_Demo.xlsx
+++ b/src/test/resources/TestDataFolder/Premium_Sauce_Demo.xlsx
@@ -13,6 +13,7 @@
   </bookViews>
   <sheets>
     <sheet name="UserInfo" sheetId="1" r:id="rId1"/>
+    <sheet name="NewUserSheet" r:id="rId5" sheetId="2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
   <si>
     <t>UserName</t>
   </si>
@@ -54,6 +55,15 @@
   </si>
   <si>
     <t>Email</t>
+  </si>
+  <si>
+    <t>NewUser</t>
+  </si>
+  <si>
+    <t>NewData1</t>
+  </si>
+  <si>
+    <t>NewData2</t>
   </si>
 </sst>
 </file>
@@ -399,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" style="3" width="24.5703125"/>
@@ -407,18 +417,18 @@
     <col min="3" max="16384" style="3" width="9.140625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="3">
+      <c r="C1" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -426,7 +436,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -434,7 +444,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -442,7 +452,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
@@ -450,7 +460,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
@@ -458,16 +468,42 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/src/test/resources/TestDataFolder/Premium_Sauce_Demo.xlsx
+++ b/src/test/resources/TestDataFolder/Premium_Sauce_Demo.xlsx
@@ -9,11 +9,10 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4545"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4545" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="UserInfo" sheetId="1" r:id="rId1"/>
-    <sheet name="NewUserSheet" r:id="rId5" sheetId="2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
   <si>
     <t>UserName</t>
   </si>
@@ -52,12 +51,6 @@
   </si>
   <si>
     <t>secret_sauce</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>NewUser</t>
   </si>
   <si>
     <t>NewData1</t>
@@ -409,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" style="3" width="24.5703125"/>
@@ -417,18 +410,15 @@
     <col min="3" max="16384" style="3" width="9.140625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -436,7 +426,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -444,7 +434,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -452,7 +442,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
@@ -460,7 +450,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
@@ -468,42 +458,16 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>12</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>